--- a/analysis/econometrics_outputs/contdid/Graficos/contracts/contdid_cosine_weighted_continuous.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/contracts/contdid_cosine_weighted_continuous.xlsx
@@ -407,7 +407,7 @@
     <col min="5" max="5" width="13.67625" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="12.4975" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="13.67625" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="13.67625" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="12.4975" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="5.425" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="3.71" hidden="0" customWidth="1"/>
@@ -515,13 +515,13 @@
         <v>653.7829</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>709.89</v>
+        <v>1259.6211</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-16452.5749</v>
+        <v>-2777.1465</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>17760.1408</v>
+        <v>4084.7124</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -543,16 +543,16 @@
         <v>-11500.953</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>327.4299</v>
+        <v>8011.6521</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-19391.0941</v>
+        <v>-33322.9224</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-3610.8119</v>
+        <v>10321.0163</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>11</v>
@@ -571,13 +571,13 @@
         <v>-145.2446</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>148.6755</v>
+        <v>1076.8106</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-3727.9062</v>
+        <v>-3078.2386</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>3437.417</v>
+        <v>2787.7495</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -599,13 +599,13 @@
         <v>-17164.897</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>927.7959</v>
+        <v>8671.7422</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>-39522.176</v>
+        <v>-40784.8058</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>5192.382</v>
+        <v>6455.0118</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -627,13 +627,13 @@
         <v>-11410.636</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>6590.1231</v>
+        <v>7800.9362</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-170214.1105</v>
+        <v>-32658.6618</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>147392.8385</v>
+        <v>9837.3898</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -655,13 +655,13 @@
         <v>5863.2482</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>198.1331</v>
+        <v>1949.4862</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1088.7968</v>
+        <v>553.2788</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>10637.6995</v>
+        <v>11173.2175</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>12</v>
@@ -683,13 +683,13 @@
         <v>11472.3328</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>4426.0587</v>
+        <v>8125.4045</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-95183.2626</v>
+        <v>-10659.473</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>118127.9282</v>
+        <v>33604.1386</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -711,13 +711,13 @@
         <v>-13666.411</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>1612.8059</v>
+        <v>5314.3612</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>-52530.5067</v>
+        <v>-28141.5563</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>25197.6847</v>
+        <v>808.7342</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -739,13 +739,13 @@
         <v>-1793.1768</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>672.6573</v>
+        <v>1802.4957</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-18002.33</v>
+        <v>-6702.7767</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>14415.9763</v>
+        <v>3116.423</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -767,13 +767,13 @@
         <v>-330.4401</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>2298.5043</v>
+        <v>2151.9731</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-55717.9437</v>
+        <v>-6191.9392</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>55057.0635</v>
+        <v>5531.0589</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -795,13 +795,13 @@
         <v>9088.2205</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>5226.1886</v>
+        <v>6776.1171</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-116848.2612</v>
+        <v>-9368.4247</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>135024.7021</v>
+        <v>27544.8656</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -823,13 +823,13 @@
         <v>13582.9181</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>9332.5128</v>
+        <v>9157.4754</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-211304.4551</v>
+        <v>-11360.0206</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>238470.2914</v>
+        <v>38525.8569</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -851,13 +851,13 @@
         <v>-2454.0239</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>5118.1609</v>
+        <v>5153.8562</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>-125787.3398</v>
+        <v>-16491.9891</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>120879.292</v>
+        <v>11583.9412</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -879,13 +879,13 @@
         <v>-10372.1981</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>9732.9883</v>
+        <v>7643.077</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-244909.9063</v>
+        <v>-31190.2504</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>224165.51</v>
+        <v>10445.8542</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -907,13 +907,13 @@
         <v>-2866.2371</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>1128.8405</v>
+        <v>1756.4606</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>-30068.126</v>
+        <v>-7650.4475</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>24335.6518</v>
+        <v>1917.9733</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -935,13 +935,13 @@
         <v>-9697.9458</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>6938.9614</v>
+        <v>5929.3919</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>-176907.4459</v>
+        <v>-25848.2987</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>157511.5544</v>
+        <v>6452.4071</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -963,13 +963,13 @@
         <v>2969.0107</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>1684.4487</v>
+        <v>2041.0215</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>-37621.4769</v>
+        <v>-2590.2808</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>43559.4982</v>
+        <v>8528.3021</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -991,16 +991,16 @@
         <v>10423.8759</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>3279.1671</v>
+        <v>3054.2074</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>-68594.8513</v>
+        <v>2104.89</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>89442.6031</v>
+        <v>18742.8618</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>11</v>
@@ -1019,13 +1019,13 @@
         <v>12625.5224</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>9495.8847</v>
+        <v>7213.3394</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>-216198.6553</v>
+        <v>-7022.0196</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>241449.7001</v>
+        <v>32273.0645</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1047,13 +1047,13 @@
         <v>-9234.8437</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>5024.3036</v>
+        <v>5182.8575</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>-130306.4625</v>
+        <v>-23351.8017</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>111836.7752</v>
+        <v>4882.1144</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1075,13 +1075,13 @@
         <v>-4768.4281</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>824.1975</v>
+        <v>3296.6252</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>-24629.2764</v>
+        <v>-13747.7065</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>15092.4202</v>
+        <v>4210.8503</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1103,13 +1103,13 @@
         <v>1061.6613</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>2064.8267</v>
+        <v>4388.7701</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>-48694.8682</v>
+        <v>-10892.3783</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>50818.1908</v>
+        <v>13015.7009</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1131,13 +1131,13 @@
         <v>2798.4448</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>9007.9214</v>
+        <v>7577.3473</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>-214267.1853</v>
+        <v>-17840.5743</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>219864.0749</v>
+        <v>23437.4639</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1159,13 +1159,13 @@
         <v>8152.4121</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>8798.5104</v>
+        <v>10913.9424</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>-203867.0012</v>
+        <v>-21574.7544</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>220171.8255</v>
+        <v>37879.5787</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1187,13 +1187,13 @@
         <v>8509.4164</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>1974.062</v>
+        <v>8477.8982</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>-39059.9385</v>
+        <v>-14582.5043</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>56078.7713</v>
+        <v>31601.3371</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1215,13 +1215,13 @@
         <v>-2937.8357</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>4174.3517</v>
+        <v>2860.9233</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>-103527.999</v>
+        <v>-10730.3582</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>97652.3276</v>
+        <v>4854.6869</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1243,13 +1243,13 @@
         <v>-4574.7315</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>1145.9893</v>
+        <v>2255.7652</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>-32189.8577</v>
+        <v>-10718.9373</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>23040.3947</v>
+        <v>1569.4743</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1271,13 +1271,13 @@
         <v>-12840.9737</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>3981.9159</v>
+        <v>4783.7341</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-108793.9738</v>
+        <v>-25870.8078</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>83112.0265</v>
+        <v>188.8605</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1299,13 +1299,13 @@
         <v>-10122.5291</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>3299.5013</v>
+        <v>4885.9335</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>-89631.2521</v>
+        <v>-23430.7319</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>69386.1938</v>
+        <v>3185.6736</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1327,13 +1327,13 @@
         <v>-4229.6909</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>1345.2344</v>
+        <v>4434.985</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-36646.0661</v>
+        <v>-16309.6096</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>28186.6844</v>
+        <v>7850.2279</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
@@ -1355,13 +1355,13 @@
         <v>3278.8116</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>1584.0819</v>
+        <v>2981.9101</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>-34893.1174</v>
+        <v>-4843.2523</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>41450.7406</v>
+        <v>11400.8754</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1383,13 +1383,13 @@
         <v>-4046.1036</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>2385.3342</v>
+        <v>2583.2071</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>-61525.9637</v>
+        <v>-11082.1885</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>53433.7566</v>
+        <v>2989.9814</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
@@ -1411,13 +1411,13 @@
         <v>-1973.692</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>2526.2835</v>
+        <v>2449.6393</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>-62850.0349</v>
+        <v>-8645.9679</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>58902.6509</v>
+        <v>4698.584</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1439,13 +1439,13 @@
         <v>4112.4147</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>1200.1926</v>
+        <v>4878.0407</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>-24808.8586</v>
+        <v>-9174.2898</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>33033.6881</v>
+        <v>17399.1192</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1467,13 +1467,13 @@
         <v>4153.4496</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>5230.9486</v>
+        <v>5038.2407</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>-121897.7332</v>
+        <v>-9569.6043</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>130204.6324</v>
+        <v>17876.5035</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1495,13 +1495,13 @@
         <v>9432.8314</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>10264.5521</v>
+        <v>9606.317</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>-237914.0741</v>
+        <v>-16732.6525</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>256779.737</v>
+        <v>35598.3153</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1523,13 +1523,13 @@
         <v>6573.8397</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>2839.3378</v>
+        <v>7318.2617</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>-61846.2345</v>
+        <v>-13359.4875</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>74993.914</v>
+        <v>26507.167</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1551,13 +1551,13 @@
         <v>2072.5019</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>2717.2404</v>
+        <v>3858.8213</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>-63405.3675</v>
+        <v>-8438.0742</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>67550.3713</v>
+        <v>12583.078</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1579,13 +1579,13 @@
         <v>-4253.8996</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>802.3898</v>
+        <v>2883.8324</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>-23589.2436</v>
+        <v>-12108.8216</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>15081.4443</v>
+        <v>3601.0224</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -1607,13 +1607,13 @@
         <v>-9128.3174</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>1156.4075</v>
+        <v>3507.5928</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>-36994.493</v>
+        <v>-18682.225</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>18737.8582</v>
+        <v>425.5901</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1635,13 +1635,13 @@
         <v>-4574.6792</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>514.4946</v>
+        <v>3633.3565</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>-16972.5564</v>
+        <v>-14471.1393</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>7823.198</v>
+        <v>5321.7809</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
@@ -1663,13 +1663,13 @@
         <v>-6993.0676</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>3965.2897</v>
+        <v>6400.0924</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>-102545.4227</v>
+        <v>-24425.5046</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>88559.2874</v>
+        <v>10439.3694</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -1691,13 +1691,13 @@
         <v>6085.8897</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>846.3574</v>
+        <v>4586.4442</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>-14308.9484</v>
+        <v>-6406.5706</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>26480.7278</v>
+        <v>18578.3499</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1719,13 +1719,13 @@
         <v>-2794.9842</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>2891.0668</v>
+        <v>2168.7516</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>-72461.5821</v>
+        <v>-8702.1842</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>66871.6138</v>
+        <v>3112.2159</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -1747,13 +1747,13 @@
         <v>612.4144</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>736.0794</v>
+        <v>2098.2518</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>-17125.0346</v>
+        <v>-5102.7596</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>18349.8634</v>
+        <v>6327.5883</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -1775,13 +1775,13 @@
         <v>4761.0268</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>3021.443</v>
+        <v>6015.6871</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>-68047.2728</v>
+        <v>-11624.3749</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>77569.3264</v>
+        <v>21146.4286</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -1803,13 +1803,13 @@
         <v>2755.3944</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>2927.7369</v>
+        <v>6004.9019</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-67794.85</v>
+        <v>-13600.6309</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>73305.6388</v>
+        <v>19111.4198</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -1831,13 +1831,13 @@
         <v>8794.4096</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>4938.503</v>
+        <v>9298.119</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-110209.6564</v>
+        <v>-16531.6112</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>127798.4756</v>
+        <v>34120.4304</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
@@ -1859,13 +1859,13 @@
         <v>9106.9894</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>1646.5945</v>
+        <v>8237.7816</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-30571.3171</v>
+        <v>-13330.9066</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>48785.2959</v>
+        <v>31544.8855</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -1887,13 +1887,13 @@
         <v>7956.4944</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>1110.4728</v>
+        <v>5482.057</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>-18802.7837</v>
+        <v>-6975.417</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>34715.7725</v>
+        <v>22888.4058</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -1915,13 +1915,13 @@
         <v>63.1593</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>2835.2736</v>
+        <v>2427.6784</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-68258.9787</v>
+        <v>-6549.2999</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>68385.2973</v>
+        <v>6675.6186</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -1943,13 +1943,13 @@
         <v>-8379.5917</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>4879.4683</v>
+        <v>3609.4715</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>-125961.0858</v>
+        <v>-18210.9942</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>109201.9023</v>
+        <v>1451.8108</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -1971,13 +1971,13 @@
         <v>-6411.7529</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>2498.4064</v>
+        <v>4343.658</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>-66616.3372</v>
+        <v>-18242.9171</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>53792.8314</v>
+        <v>5419.4113</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -1999,13 +1999,13 @@
         <v>-4770.5861</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>2031.1477</v>
+        <v>4433.5329</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>-53715.5454</v>
+        <v>-16846.5497</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>44174.3732</v>
+        <v>7305.3775</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2027,13 +2027,13 @@
         <v>7418.7829</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>4981.7994</v>
+        <v>4748.8852</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>-112628.6055</v>
+        <v>-5516.1307</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>127466.1712</v>
+        <v>20353.6964</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2055,13 +2055,13 @@
         <v>-4570.7825</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>227.2894</v>
+        <v>2733.9044</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>-10047.8203</v>
+        <v>-12017.3338</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>906.2552</v>
+        <v>2875.7688</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>10</v>
@@ -2083,13 +2083,13 @@
         <v>-748.1392</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>2408.2023</v>
+        <v>2412.3312</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>-58779.0584</v>
+        <v>-7318.796</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>57282.7799</v>
+        <v>5822.5176</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2111,13 +2111,13 @@
         <v>6895.2178</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>6664.5877</v>
+        <v>4791.882</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>-153702.6452</v>
+        <v>-6156.8096</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>167493.0808</v>
+        <v>19947.2452</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2139,13 +2139,13 @@
         <v>3266.3609</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>6947.2277</v>
+        <v>4717.3787</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>-164142.3339</v>
+        <v>-9582.7359</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>170675.0557</v>
+        <v>16115.4576</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2167,13 +2167,13 @@
         <v>11213.7602</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>4541.1643</v>
+        <v>10044.0275</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>-98215.5568</v>
+        <v>-16143.9505</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>120643.0771</v>
+        <v>38571.4708</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2195,13 +2195,13 @@
         <v>10111.4263</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>11611.6255</v>
+        <v>8928.0791</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>-269696.1666</v>
+        <v>-14206.6876</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>289919.0192</v>
+        <v>34429.5402</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2223,13 +2223,13 @@
         <v>-355.9875</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>212.4424</v>
+        <v>3599.1397</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>-5475.2524</v>
+        <v>-10159.2485</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>4763.2774</v>
+        <v>9447.2735</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
